--- a/Input/urbs_intertemporal_2050/2050.xlsx
+++ b/Input/urbs_intertemporal_2050/2050.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maxoi\GitHub\urbs-extension\Input\urbs_intertemporal_2050\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{775CCAA8-8924-4C2C-BC27-0ABFAC09D007}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB451F96-BD33-450C-BCD5-040B891B8075}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="67080" yWindow="-1935" windowWidth="29040" windowHeight="17520" tabRatio="796" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-5445" windowWidth="38640" windowHeight="21120" tabRatio="796" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Global" sheetId="1" r:id="rId1"/>
@@ -2623,7 +2623,7 @@
         <v>23</v>
       </c>
       <c r="D5">
-        <v>8</v>
+        <v>20.52</v>
       </c>
       <c r="E5" s="7" t="s">
         <v>24</v>
@@ -3266,13 +3266,13 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:K1" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
-  <conditionalFormatting sqref="A2:A12 B2:B3 C2:C12 P2:XFD4">
-    <cfRule type="expression" dxfId="13" priority="3">
+  <conditionalFormatting sqref="A4:C4 E4:F4">
+    <cfRule type="expression" dxfId="13" priority="14">
       <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:F3 A4:C4 E4:F4">
-    <cfRule type="expression" dxfId="12" priority="14">
+  <conditionalFormatting sqref="A2:F3 P2:XFD4 A2:A12 C2:C12">
+    <cfRule type="expression" dxfId="12" priority="3">
       <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3889,7 +3889,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:E1" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
-  <conditionalFormatting sqref="A30:C31 E30:E31 A2:C19 E2:XFD19">
+  <conditionalFormatting sqref="A2:C19 E2:XFD19 A30:C31 E30:E31">
     <cfRule type="expression" dxfId="6" priority="5">
       <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
     </cfRule>
@@ -3909,10 +3909,21 @@
       <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D4:D5 D8:D13 D15:D19 D2">
+  <conditionalFormatting sqref="D2 D4:D5 D8:D13 D15:D19">
     <cfRule type="expression" dxfId="2" priority="13">
       <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
     </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D4">
+    <cfRule type="dataBar" priority="15">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D4:D5 D8:D13 D15:D19 D2">
     <cfRule type="dataBar" priority="19">
       <dataBar>
         <cfvo type="num" val="0"/>
@@ -3930,16 +3941,7 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D4">
-    <cfRule type="dataBar" priority="15">
-      <dataBar>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="2"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D13 D15">
+  <conditionalFormatting sqref="D15 D13">
     <cfRule type="dataBar" priority="14">
       <dataBar>
         <cfvo type="num" val="0"/>

--- a/Input/urbs_intertemporal_2050/2050.xlsx
+++ b/Input/urbs_intertemporal_2050/2050.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maxoi\GitHub\urbs-extension\Input\urbs_intertemporal_2050\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB451F96-BD33-450C-BCD5-040B891B8075}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B8A6B71-77F2-45F4-9709-41E4288B0FD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-5445" windowWidth="38640" windowHeight="21120" tabRatio="796" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-5445" windowWidth="38640" windowHeight="21120" tabRatio="796" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Global" sheetId="1" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="99">
   <si>
     <t>Property</t>
   </si>
@@ -188,9 +188,6 @@
     <t>Coal Plant</t>
   </si>
   <si>
-    <t>Coal Lignite</t>
-  </si>
-  <si>
     <t>Gas Plant (CCGT)</t>
   </si>
   <si>
@@ -326,36 +323,44 @@
     <t>EU27.Gas plant</t>
   </si>
   <si>
-    <t>Coal CCUS</t>
-  </si>
-  <si>
-    <t>Coal Lignite CCUS</t>
-  </si>
-  <si>
     <t>Gas Plant (CCGT) CCUS</t>
   </si>
   <si>
-    <t>Piped Gas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LNG </t>
-  </si>
-  <si>
-    <t>Gas Plant (CCGT) LNG</t>
+    <t>Gas</t>
+  </si>
+  <si>
+    <t>Oil</t>
+  </si>
+  <si>
+    <t>Slack</t>
+  </si>
+  <si>
+    <t>Lignite Plant</t>
+  </si>
+  <si>
+    <t>Other non-res</t>
+  </si>
+  <si>
+    <t>Oil Plant</t>
+  </si>
+  <si>
+    <t>Coal Plant CCUS</t>
+  </si>
+  <si>
+    <t>Lignite Plant CCUS</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="7">
+  <numFmts count="6">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="#,##0.000"/>
     <numFmt numFmtId="168" formatCode="_-* #,##0.00\ _€_-;\-* #,##0.00\ _€_-;_-* &quot;-&quot;??\ _€_-;_-@_-"/>
-    <numFmt numFmtId="169" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="29">
     <font>
@@ -547,7 +552,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="41">
+  <fills count="40">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -745,12 +750,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00B0F0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1266,7 +1265,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="168" fontId="20" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1397,18 +1396,16 @@
     <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="166" fontId="0" fillId="37" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="37" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="24" fillId="38" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="24" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="3" fontId="0" fillId="37" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="3" fontId="0" fillId="37" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="39" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="38" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="28" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="40" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="39" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1416,9 +1413,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="363">
     <cellStyle name="20% - Akzent1" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
@@ -1785,132 +1780,826 @@
     <cellStyle name="Zelle überprüfen 4" xfId="214" xr:uid="{00000000-0005-0000-0000-0000D6000000}"/>
     <cellStyle name="Zelle überprüfen 5" xfId="215" xr:uid="{00000000-0005-0000-0000-0000D7000000}"/>
   </cellStyles>
-  <dxfs count="15">
-    <dxf>
-      <border>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <vertical/>
-        <horizontal/>
-      </border>
+  <dxfs count="92">
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <border>
@@ -2260,7 +2949,7 @@
       <c r="A3" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="63">
+      <c r="B3" s="61">
         <v>0</v>
       </c>
       <c r="C3" s="29" t="s">
@@ -2301,10 +2990,10 @@
   <sheetData>
     <row r="1" spans="1:2" s="15" customFormat="1">
       <c r="A1" s="13" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -2319,7 +3008,7 @@
       <c r="A3" s="5">
         <v>1</v>
       </c>
-      <c r="B3" s="62">
+      <c r="B3" s="60">
         <v>0.20699999999999999</v>
       </c>
     </row>
@@ -2327,7 +3016,7 @@
       <c r="A4" s="5">
         <v>2</v>
       </c>
-      <c r="B4" s="62">
+      <c r="B4" s="60">
         <v>0.20699999999999999</v>
       </c>
     </row>
@@ -2335,7 +3024,7 @@
       <c r="A5" s="5">
         <v>3</v>
       </c>
-      <c r="B5" s="62">
+      <c r="B5" s="60">
         <v>0.20699999999999999</v>
       </c>
     </row>
@@ -2343,7 +3032,7 @@
       <c r="A6" s="5">
         <v>4</v>
       </c>
-      <c r="B6" s="62">
+      <c r="B6" s="60">
         <v>0.20699999999999999</v>
       </c>
     </row>
@@ -2351,7 +3040,7 @@
       <c r="A7" s="5">
         <v>5</v>
       </c>
-      <c r="B7" s="62">
+      <c r="B7" s="60">
         <v>0.20699999999999999</v>
       </c>
     </row>
@@ -2359,7 +3048,7 @@
       <c r="A8" s="5">
         <v>6</v>
       </c>
-      <c r="B8" s="62">
+      <c r="B8" s="60">
         <v>0.20699999999999999</v>
       </c>
     </row>
@@ -2367,7 +3056,7 @@
       <c r="A9" s="5">
         <v>7</v>
       </c>
-      <c r="B9" s="62">
+      <c r="B9" s="60">
         <v>0.20699999999999999</v>
       </c>
     </row>
@@ -2375,7 +3064,7 @@
       <c r="A10" s="5">
         <v>8</v>
       </c>
-      <c r="B10" s="62">
+      <c r="B10" s="60">
         <v>0.20699999999999999</v>
       </c>
     </row>
@@ -2383,7 +3072,7 @@
       <c r="A11" s="5">
         <v>9</v>
       </c>
-      <c r="B11" s="62">
+      <c r="B11" s="60">
         <v>0.20699999999999999</v>
       </c>
     </row>
@@ -2391,7 +3080,7 @@
       <c r="A12" s="5">
         <v>10</v>
       </c>
-      <c r="B12" s="62">
+      <c r="B12" s="60">
         <v>0.20699999999999999</v>
       </c>
     </row>
@@ -2399,7 +3088,7 @@
       <c r="A13" s="5">
         <v>11</v>
       </c>
-      <c r="B13" s="62">
+      <c r="B13" s="60">
         <v>0.20699999999999999</v>
       </c>
     </row>
@@ -2407,7 +3096,7 @@
       <c r="A14" s="5">
         <v>12</v>
       </c>
-      <c r="B14" s="62">
+      <c r="B14" s="60">
         <v>0.20699999999999999</v>
       </c>
     </row>
@@ -2431,13 +3120,13 @@
   <sheetData>
     <row r="1" spans="1:3" s="15" customFormat="1">
       <c r="A1" s="15" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B1" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="C1" s="15" t="s">
         <v>87</v>
-      </c>
-      <c r="C1" s="15" t="s">
-        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -2456,13 +3145,13 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B1" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C1" s="6" t="s">
         <v>89</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -2514,7 +3203,7 @@
   <sheetPr>
     <tabColor theme="4" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="10.6640625" style="3" customWidth="1"/>
@@ -2617,7 +3306,7 @@
         <v>11</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>23</v>
@@ -2703,7 +3392,7 @@
         <v>23</v>
       </c>
       <c r="D9">
-        <v>5.76</v>
+        <v>6.48</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>24</v>
@@ -2717,13 +3406,13 @@
         <v>11</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>23</v>
       </c>
       <c r="D10">
-        <v>36.54</v>
+        <v>32.04</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>24</v>
@@ -2732,11 +3421,34 @@
         <v>24</v>
       </c>
     </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D11">
+        <v>32.04</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="B8:B10">
-    <cfRule type="expression" dxfId="14" priority="1">
+  <conditionalFormatting sqref="B8:B11">
+    <cfRule type="expression" dxfId="91" priority="1">
       <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
     </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2:B11">
+    <cfRule type="duplicateValues" dxfId="90" priority="2"/>
   </conditionalFormatting>
   <dataValidations xWindow="307" yWindow="342" count="3">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Commodity price (€/MWh)" prompt="Cost for purchasing one unit (MWh) of a stock or buy commodity. Revenue for selling one unit (MWh) of a sell commodity. Cost for creating one unit of environmental commodity._x000a__x000a_Multiplier for sheet &quot;Buy-Sell-Price&quot; for commodity types &quot;Buy&quot; and &quot;Sell&quot;._x000a_" sqref="D1" xr:uid="{6446A307-7646-432D-BFA5-6520C4C5055D}"/>
@@ -2753,7 +3465,7 @@
   <sheetPr>
     <tabColor theme="4" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="10.6640625" style="3" customWidth="1"/>
@@ -2817,38 +3529,38 @@
       <c r="A2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="49" t="s">
-        <v>42</v>
+      <c r="B2" s="3" t="s">
+        <v>44</v>
       </c>
       <c r="C2" s="20">
         <v>0</v>
       </c>
-      <c r="D2" s="54">
-        <v>46710</v>
+      <c r="D2" s="20">
+        <v>56122</v>
       </c>
       <c r="E2" s="50" t="s">
         <v>24</v>
       </c>
       <c r="F2" s="51">
-        <v>0</v>
-      </c>
-      <c r="G2" s="52">
-        <v>2620279.14</v>
-      </c>
-      <c r="H2" s="52">
-        <v>9143.1016799999998</v>
+        <v>0.5</v>
+      </c>
+      <c r="G2" s="54">
+        <v>1784013.3448000001</v>
+      </c>
+      <c r="H2" s="55">
+        <v>28544.213516799999</v>
       </c>
       <c r="I2" s="52">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="J2" s="53">
         <v>0</v>
       </c>
-      <c r="K2" s="59">
+      <c r="K2" s="57">
         <v>7.2999999999999995E-2</v>
       </c>
       <c r="L2" s="53">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="M2" s="28" t="e">
         <v>#N/A</v>
@@ -2858,38 +3570,38 @@
       <c r="A3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="49" t="s">
-        <v>43</v>
+      <c r="B3" s="3" t="s">
+        <v>94</v>
       </c>
       <c r="C3" s="20">
         <v>0</v>
       </c>
-      <c r="D3" s="54">
-        <v>59840</v>
+      <c r="D3" s="20">
+        <v>43599</v>
       </c>
       <c r="E3" s="50" t="s">
         <v>24</v>
       </c>
       <c r="F3" s="51">
-        <v>0</v>
-      </c>
-      <c r="G3" s="53">
-        <v>3345037.2</v>
-      </c>
-      <c r="H3" s="53">
-        <v>28432.799999999999</v>
+        <v>0.65</v>
+      </c>
+      <c r="G3" s="52">
+        <v>2230016.6809999999</v>
+      </c>
+      <c r="H3" s="52">
+        <v>43931.328608800002</v>
       </c>
       <c r="I3" s="53">
-        <v>0.35699999999999998</v>
+        <v>3.2</v>
       </c>
       <c r="J3" s="53">
         <v>0</v>
       </c>
-      <c r="K3" s="59">
+      <c r="K3" s="57">
         <v>7.2999999999999995E-2</v>
       </c>
       <c r="L3" s="53">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="M3" s="28" t="e">
         <v>#N/A</v>
@@ -2899,38 +3611,38 @@
       <c r="A4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="49" t="s">
-        <v>44</v>
+      <c r="B4" s="3" t="s">
+        <v>45</v>
       </c>
       <c r="C4" s="20">
         <v>0</v>
       </c>
-      <c r="D4" s="65">
+      <c r="D4" s="20">
         <v>999999</v>
       </c>
       <c r="E4" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="F4" s="51">
-        <v>0.5</v>
-      </c>
-      <c r="G4" s="56">
-        <v>1784013.3448000001</v>
-      </c>
-      <c r="H4" s="57">
-        <v>28544.213516799999</v>
-      </c>
-      <c r="I4" s="52">
-        <v>2.7</v>
-      </c>
-      <c r="J4" s="53">
+      <c r="F4" s="3">
         <v>0</v>
       </c>
-      <c r="K4" s="59">
+      <c r="G4" s="52">
+        <v>735908.18400000012</v>
+      </c>
+      <c r="H4" s="52">
+        <v>16725.186000000002</v>
+      </c>
+      <c r="I4" s="53">
+        <v>2.6</v>
+      </c>
+      <c r="J4" s="54">
+        <v>0</v>
+      </c>
+      <c r="K4" s="57">
         <v>7.2999999999999995E-2</v>
       </c>
       <c r="L4" s="53">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="M4" s="28" t="e">
         <v>#N/A</v>
@@ -2940,38 +3652,38 @@
       <c r="A5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="49" t="s">
-        <v>45</v>
+      <c r="B5" s="3" t="s">
+        <v>95</v>
       </c>
       <c r="C5" s="20">
         <v>0</v>
       </c>
-      <c r="D5" s="65">
-        <v>999999</v>
+      <c r="D5" s="20">
+        <v>13483</v>
       </c>
       <c r="E5" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="F5" s="51">
-        <v>0.65</v>
-      </c>
-      <c r="G5" s="52">
-        <v>2230016.6809999999</v>
-      </c>
-      <c r="H5" s="52">
-        <v>43931.328608800002</v>
-      </c>
-      <c r="I5" s="53">
-        <v>3.2</v>
-      </c>
-      <c r="J5" s="53">
+      <c r="F5" s="3">
         <v>0</v>
       </c>
-      <c r="K5" s="59">
-        <v>7.2999999999999995E-2</v>
+      <c r="G5">
+        <v>5648000</v>
+      </c>
+      <c r="H5" s="63">
+        <v>16725.186000000002</v>
+      </c>
+      <c r="I5">
+        <v>2.6</v>
+      </c>
+      <c r="J5" s="54">
+        <v>0</v>
+      </c>
+      <c r="K5" s="43">
+        <v>7.0999999999999994E-2</v>
       </c>
       <c r="L5" s="53">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="M5" s="28" t="e">
         <v>#N/A</v>
@@ -2981,35 +3693,35 @@
       <c r="A6" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="49" t="s">
-        <v>46</v>
+      <c r="B6" s="3" t="s">
+        <v>96</v>
       </c>
       <c r="C6" s="20">
         <v>0</v>
       </c>
-      <c r="D6" s="65">
-        <v>999999</v>
+      <c r="D6" s="20">
+        <v>14578</v>
       </c>
       <c r="E6" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="F6" s="51">
-        <v>0.25</v>
-      </c>
-      <c r="G6" s="52">
-        <v>735908.18400000012</v>
-      </c>
-      <c r="H6" s="52">
+      <c r="F6" s="3">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>5648000</v>
+      </c>
+      <c r="H6" s="63">
         <v>16725.186000000002</v>
       </c>
-      <c r="I6" s="53">
+      <c r="I6">
         <v>2.6</v>
       </c>
-      <c r="J6" s="56">
+      <c r="J6" s="54">
         <v>0</v>
       </c>
-      <c r="K6" s="59">
-        <v>7.2999999999999995E-2</v>
+      <c r="K6" s="43">
+        <v>7.0999999999999994E-2</v>
       </c>
       <c r="L6" s="53">
         <v>25</v>
@@ -3022,38 +3734,38 @@
       <c r="A7" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="49" t="s">
-        <v>47</v>
+      <c r="B7" s="3" t="s">
+        <v>97</v>
       </c>
       <c r="C7" s="20">
         <v>0</v>
       </c>
-      <c r="D7" s="55">
-        <v>94200</v>
+      <c r="D7" s="20">
+        <v>100000</v>
       </c>
       <c r="E7" s="50" t="s">
         <v>24</v>
       </c>
       <c r="F7" s="51">
+        <v>0.5</v>
+      </c>
+      <c r="G7" s="53">
+        <v>3177785.3400000003</v>
+      </c>
+      <c r="H7" s="53">
+        <v>60099.168360000003</v>
+      </c>
+      <c r="I7" s="53">
+        <v>6.22</v>
+      </c>
+      <c r="J7" s="54">
         <v>0</v>
       </c>
-      <c r="G7" s="52">
-        <v>5240558.28</v>
-      </c>
-      <c r="H7" s="57">
-        <v>117076.302</v>
-      </c>
-      <c r="I7" s="52">
-        <v>8.6999999999999993</v>
-      </c>
-      <c r="J7" s="53">
-        <v>0</v>
-      </c>
-      <c r="K7" s="59">
-        <v>7.2999999999999995E-2</v>
+      <c r="K7" s="43">
+        <v>7.0999999999999994E-2</v>
       </c>
       <c r="L7" s="53">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="M7" s="28" t="e">
         <v>#N/A</v>
@@ -3063,38 +3775,38 @@
       <c r="A8" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="49" t="s">
-        <v>48</v>
+      <c r="B8" s="3" t="s">
+        <v>98</v>
       </c>
       <c r="C8" s="20">
         <v>0</v>
       </c>
       <c r="D8" s="20">
-        <v>999999999999</v>
+        <v>100000</v>
       </c>
       <c r="E8" s="50" t="s">
         <v>24</v>
       </c>
       <c r="F8" s="51">
+        <v>0.65</v>
+      </c>
+      <c r="G8" s="53">
+        <v>3568039.68</v>
+      </c>
+      <c r="H8" s="53">
+        <v>67569.751440000007</v>
+      </c>
+      <c r="I8" s="53">
+        <v>4.5</v>
+      </c>
+      <c r="J8" s="54">
         <v>0</v>
       </c>
-      <c r="G8" s="58">
-        <v>5648000</v>
-      </c>
-      <c r="H8" s="58">
-        <v>0</v>
-      </c>
-      <c r="I8" s="58">
-        <v>53.2</v>
-      </c>
-      <c r="J8" s="53">
-        <v>0</v>
-      </c>
-      <c r="K8" s="59">
-        <v>7.2999999999999995E-2</v>
+      <c r="K8" s="43">
+        <v>7.0999999999999994E-2</v>
       </c>
       <c r="L8" s="53">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="M8" s="28" t="e">
         <v>#N/A</v>
@@ -3104,38 +3816,38 @@
       <c r="A9" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="49" t="s">
-        <v>91</v>
+      <c r="B9" s="3" t="s">
+        <v>90</v>
       </c>
       <c r="C9" s="20">
         <v>0</v>
       </c>
-      <c r="D9" s="55">
-        <v>0</v>
+      <c r="D9" s="20">
+        <v>100000</v>
       </c>
       <c r="E9" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="F9" s="51">
-        <v>0.5</v>
+      <c r="F9" s="3">
+        <v>0</v>
       </c>
       <c r="G9" s="53">
-        <v>3177785.3400000003</v>
+        <v>1672518.6</v>
       </c>
       <c r="H9" s="53">
-        <v>60099.168360000003</v>
+        <v>38244.9</v>
       </c>
       <c r="I9" s="53">
-        <v>6.22</v>
-      </c>
-      <c r="J9" s="56">
+        <v>3.1</v>
+      </c>
+      <c r="J9" s="54">
         <v>0</v>
       </c>
       <c r="K9" s="43">
         <v>7.0999999999999994E-2</v>
       </c>
       <c r="L9" s="53">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="M9" s="28" t="e">
         <v>#N/A</v>
@@ -3146,37 +3858,37 @@
         <v>11</v>
       </c>
       <c r="B10" s="49" t="s">
-        <v>92</v>
+        <v>46</v>
       </c>
       <c r="C10" s="20">
         <v>0</v>
       </c>
-      <c r="D10" s="55">
-        <v>0</v>
+      <c r="D10" s="20">
+        <v>94198</v>
       </c>
       <c r="E10" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="F10" s="51">
-        <v>0.65</v>
-      </c>
-      <c r="G10" s="53">
-        <v>3568039.68</v>
-      </c>
-      <c r="H10" s="53">
-        <v>67569.751440000007</v>
-      </c>
-      <c r="I10" s="53">
-        <v>4.5</v>
-      </c>
-      <c r="J10" s="56">
+      <c r="F10" s="3">
         <v>0</v>
       </c>
-      <c r="K10" s="43">
-        <v>7.0999999999999994E-2</v>
+      <c r="G10" s="52">
+        <v>5240558.28</v>
+      </c>
+      <c r="H10" s="55">
+        <v>117076.302</v>
+      </c>
+      <c r="I10" s="52">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="J10" s="53">
+        <v>0</v>
+      </c>
+      <c r="K10" s="57">
+        <v>7.2999999999999995E-2</v>
       </c>
       <c r="L10" s="53">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="M10" s="28" t="e">
         <v>#N/A</v>
@@ -3187,37 +3899,37 @@
         <v>11</v>
       </c>
       <c r="B11" s="49" t="s">
-        <v>93</v>
+        <v>42</v>
       </c>
       <c r="C11" s="20">
         <v>0</v>
       </c>
-      <c r="D11" s="55">
-        <v>0</v>
+      <c r="D11" s="20">
+        <v>46703</v>
       </c>
       <c r="E11" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="F11" s="51">
-        <v>0.25</v>
-      </c>
-      <c r="G11" s="53">
-        <v>1672518.6</v>
-      </c>
-      <c r="H11" s="53">
-        <v>38244.9</v>
-      </c>
-      <c r="I11" s="53">
-        <v>3.1</v>
-      </c>
-      <c r="J11" s="56">
+      <c r="F11" s="3">
         <v>0</v>
       </c>
-      <c r="K11" s="43">
-        <v>7.0999999999999994E-2</v>
+      <c r="G11" s="52">
+        <v>2620279.14</v>
+      </c>
+      <c r="H11" s="52">
+        <v>9143.1016799999998</v>
+      </c>
+      <c r="I11" s="52">
+        <v>0</v>
+      </c>
+      <c r="J11" s="53">
+        <v>0</v>
+      </c>
+      <c r="K11" s="57">
+        <v>7.2999999999999995E-2</v>
       </c>
       <c r="L11" s="53">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="M11" s="28" t="e">
         <v>#N/A</v>
@@ -3227,77 +3939,163 @@
       <c r="A12" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="60" t="s">
-        <v>96</v>
+      <c r="B12" s="49" t="s">
+        <v>43</v>
       </c>
       <c r="C12" s="20">
         <v>0</v>
       </c>
-      <c r="D12" s="65">
-        <v>999999</v>
+      <c r="D12" s="20">
+        <v>61218</v>
       </c>
       <c r="E12" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="F12" s="51">
-        <v>0.25</v>
-      </c>
-      <c r="G12" s="52">
-        <v>735908.18400000012</v>
-      </c>
-      <c r="H12" s="52">
-        <v>16725.186000000002</v>
+      <c r="F12" s="3">
+        <v>0</v>
+      </c>
+      <c r="G12" s="53">
+        <v>3345037.2</v>
+      </c>
+      <c r="H12" s="53">
+        <v>28432.799999999999</v>
       </c>
       <c r="I12" s="53">
-        <v>2.6</v>
-      </c>
-      <c r="J12" s="56">
+        <v>0.35699999999999998</v>
+      </c>
+      <c r="J12" s="53">
         <v>0</v>
       </c>
-      <c r="K12" s="59">
+      <c r="K12" s="57">
         <v>7.2999999999999995E-2</v>
       </c>
       <c r="L12" s="53">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="M12" s="28" t="e">
         <v>#N/A</v>
       </c>
     </row>
+    <row r="13" spans="1:13">
+      <c r="A13" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="49" t="s">
+        <v>47</v>
+      </c>
+      <c r="C13" s="20">
+        <v>0</v>
+      </c>
+      <c r="D13" s="20">
+        <v>999999</v>
+      </c>
+      <c r="E13" s="50" t="s">
+        <v>24</v>
+      </c>
+      <c r="F13" s="3">
+        <v>0</v>
+      </c>
+      <c r="G13" s="56">
+        <v>5648000</v>
+      </c>
+      <c r="H13" s="56">
+        <v>0</v>
+      </c>
+      <c r="I13" s="56">
+        <v>53.2</v>
+      </c>
+      <c r="J13" s="53">
+        <v>0</v>
+      </c>
+      <c r="K13" s="57">
+        <v>7.2999999999999995E-2</v>
+      </c>
+      <c r="L13" s="53">
+        <v>25</v>
+      </c>
+      <c r="M13" s="28" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
-  <conditionalFormatting sqref="A4:C4 E4:F4">
-    <cfRule type="expression" dxfId="13" priority="14">
+  <conditionalFormatting sqref="P2:XFD4">
+    <cfRule type="expression" dxfId="89" priority="30">
       <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:F3 P2:XFD4 A2:A12 C2:C12">
-    <cfRule type="expression" dxfId="12" priority="3">
+  <conditionalFormatting sqref="A1:XFD1 A14:XFD1048576 N13:XFD13">
+    <cfRule type="expression" dxfId="88" priority="47">
       <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:XFD1 A13:XFD1048576">
-    <cfRule type="expression" dxfId="11" priority="20">
+  <conditionalFormatting sqref="N12:XFD12">
+    <cfRule type="expression" dxfId="87" priority="31">
       <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B5:B12">
-    <cfRule type="expression" dxfId="10" priority="1">
+  <conditionalFormatting sqref="C2:D13 F9:F13 F4:F6">
+    <cfRule type="expression" dxfId="86" priority="13">
       <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D8">
-    <cfRule type="expression" dxfId="9" priority="9">
+  <conditionalFormatting sqref="E2:E4 E12:E13">
+    <cfRule type="expression" dxfId="85" priority="12">
       <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:I2">
-    <cfRule type="expression" dxfId="8" priority="8">
+  <conditionalFormatting sqref="F2">
+    <cfRule type="expression" dxfId="84" priority="11">
       <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N12:XFD12">
-    <cfRule type="expression" dxfId="7" priority="4">
+  <conditionalFormatting sqref="F7">
+    <cfRule type="expression" dxfId="83" priority="10">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2:B9">
+    <cfRule type="expression" dxfId="82" priority="9">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2:A4">
+    <cfRule type="expression" dxfId="81" priority="8">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2:A13">
+    <cfRule type="expression" dxfId="80" priority="7">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B10">
+    <cfRule type="expression" dxfId="79" priority="6">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B11:B12">
+    <cfRule type="expression" dxfId="78" priority="5">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B11:B12">
+    <cfRule type="expression" dxfId="77" priority="4">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B13">
+    <cfRule type="expression" dxfId="76" priority="3">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M2">
+    <cfRule type="expression" dxfId="75" priority="2">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G11:I11">
+    <cfRule type="expression" dxfId="74" priority="1">
       <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3324,7 +4122,7 @@
   <sheetPr>
     <tabColor theme="4" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="16.33203125" style="3" bestFit="1" customWidth="1"/>
@@ -3344,24 +4142,24 @@
         <v>13</v>
       </c>
       <c r="C1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D1" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="D1" s="18" t="s">
+      <c r="E1" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="E1" s="18" t="s">
-        <v>51</v>
-      </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="60" t="s">
-        <v>45</v>
+      <c r="A2" s="3" t="s">
+        <v>94</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>22</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D2" s="24">
         <v>1</v>
@@ -3371,16 +4169,16 @@
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="60" t="s">
-        <v>45</v>
+      <c r="A3" s="3" t="s">
+        <v>94</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>20</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D3" s="61">
+        <v>52</v>
+      </c>
+      <c r="D3" s="59">
         <v>0.44</v>
       </c>
       <c r="E3" s="24" t="e">
@@ -3389,14 +4187,14 @@
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="60" t="s">
-        <v>45</v>
+      <c r="A4" s="3" t="s">
+        <v>94</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>25</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D4" s="24">
         <v>0.36299999999999999</v>
@@ -3406,14 +4204,14 @@
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="60" t="s">
-        <v>46</v>
+      <c r="A5" s="58" t="s">
+        <v>45</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D5" s="24">
         <v>1</v>
@@ -3423,16 +4221,16 @@
       </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="60" t="s">
-        <v>46</v>
+      <c r="A6" s="58" t="s">
+        <v>45</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>20</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D6" s="61">
+        <v>52</v>
+      </c>
+      <c r="D6" s="59">
         <v>0.63</v>
       </c>
       <c r="E6" s="24" t="e">
@@ -3441,14 +4239,14 @@
       </c>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="60" t="s">
-        <v>46</v>
+      <c r="A7" s="58" t="s">
+        <v>45</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>25</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D7" s="48">
         <v>0.01</v>
@@ -3459,14 +4257,14 @@
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="60" t="s">
-        <v>48</v>
+      <c r="A8" s="58" t="s">
+        <v>47</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>27</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D8" s="24">
         <v>1</v>
@@ -3477,14 +4275,14 @@
       </c>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="60" t="s">
-        <v>48</v>
+      <c r="A9" s="58" t="s">
+        <v>47</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>20</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D9" s="24">
         <v>0.35</v>
@@ -3495,14 +4293,14 @@
       </c>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="60" t="s">
-        <v>48</v>
+      <c r="A10" s="58" t="s">
+        <v>47</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>25</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D10" s="24">
         <v>0</v>
@@ -3513,14 +4311,14 @@
       </c>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="60" t="s">
-        <v>47</v>
+      <c r="A11" s="58" t="s">
+        <v>46</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>28</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D11" s="24">
         <v>1</v>
@@ -3531,14 +4329,14 @@
       </c>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="60" t="s">
-        <v>47</v>
+      <c r="A12" s="58" t="s">
+        <v>46</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>20</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D12" s="24">
         <v>0.38</v>
@@ -3549,14 +4347,14 @@
       </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="60" t="s">
+      <c r="A13" s="58" t="s">
         <v>44</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>29</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D13" s="24">
         <v>1</v>
@@ -3566,16 +4364,16 @@
       </c>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="60" t="s">
+      <c r="A14" s="58" t="s">
         <v>44</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>20</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D14" s="61">
+        <v>52</v>
+      </c>
+      <c r="D14" s="59">
         <v>0.47</v>
       </c>
       <c r="E14" s="24" t="e">
@@ -3584,14 +4382,14 @@
       </c>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="60" t="s">
+      <c r="A15" s="58" t="s">
         <v>44</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>25</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D15" s="24">
         <v>0.34179999999999999</v>
@@ -3602,14 +4400,14 @@
       </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="60" t="s">
+      <c r="A16" s="58" t="s">
         <v>42</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>19</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D16" s="24">
         <v>1</v>
@@ -3620,14 +4418,14 @@
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="60" t="s">
+      <c r="A17" s="58" t="s">
         <v>42</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>20</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D17" s="24">
         <v>1</v>
@@ -3638,14 +4436,14 @@
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="60" t="s">
+      <c r="A18" s="58" t="s">
         <v>43</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>19</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D18" s="24">
         <v>1</v>
@@ -3656,14 +4454,14 @@
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="60" t="s">
+      <c r="A19" s="58" t="s">
         <v>43</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>20</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D19" s="24">
         <v>1</v>
@@ -3674,14 +4472,14 @@
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="60" t="s">
-        <v>91</v>
+      <c r="A20" s="3" t="s">
+        <v>97</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>29</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D20" s="24">
         <v>1</v>
@@ -3692,14 +4490,14 @@
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="60" t="s">
-        <v>91</v>
+      <c r="A21" s="3" t="s">
+        <v>97</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>20</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D21" s="24">
         <v>0.39</v>
@@ -3710,14 +4508,14 @@
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="60" t="s">
-        <v>91</v>
+      <c r="A22" s="3" t="s">
+        <v>97</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>25</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D22" s="24">
         <v>3.4180000000000002E-2</v>
@@ -3728,14 +4526,14 @@
       </c>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="60" t="s">
-        <v>92</v>
+      <c r="A23" s="3" t="s">
+        <v>98</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>29</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D23" s="24">
         <v>1</v>
@@ -3746,14 +4544,14 @@
       </c>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="60" t="s">
-        <v>92</v>
+      <c r="A24" s="3" t="s">
+        <v>98</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>20</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D24" s="24">
         <v>0.35</v>
@@ -3764,14 +4562,14 @@
       </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="60" t="s">
-        <v>92</v>
+      <c r="A25" s="3" t="s">
+        <v>98</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>25</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D25" s="24">
         <v>3.6299999999999999E-2</v>
@@ -3782,14 +4580,14 @@
       </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="60" t="s">
-        <v>93</v>
+      <c r="A26" s="58" t="s">
+        <v>90</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D26" s="24">
         <v>1</v>
@@ -3799,14 +4597,14 @@
       </c>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="60" t="s">
-        <v>93</v>
+      <c r="A27" s="58" t="s">
+        <v>90</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>20</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D27" s="24">
         <v>0.5</v>
@@ -3817,14 +4615,14 @@
       </c>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" s="60" t="s">
-        <v>93</v>
+      <c r="A28" s="58" t="s">
+        <v>90</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>25</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D28" s="24">
         <v>1E-3</v>
@@ -3835,34 +4633,35 @@
       </c>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="60" t="s">
-        <v>96</v>
+      <c r="A29" s="3" t="s">
+        <v>95</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D29" s="24">
         <v>1</v>
       </c>
-      <c r="E29" s="24">
-        <v>1.2</v>
+      <c r="E29" s="24" t="e">
+        <f>D29*E27</f>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="60" t="s">
-        <v>96</v>
+      <c r="A30" s="3" t="s">
+        <v>95</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>20</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D30" s="61">
-        <v>0.63</v>
+        <v>52</v>
+      </c>
+      <c r="D30" s="24">
+        <v>0.4</v>
       </c>
       <c r="E30" s="24" t="e">
         <f>NA()</f>
@@ -3870,52 +4669,96 @@
       </c>
     </row>
     <row r="31" spans="1:5">
-      <c r="A31" s="60" t="s">
-        <v>96</v>
+      <c r="A31" s="3" t="s">
+        <v>95</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>25</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D31" s="48">
-        <v>0.01</v>
-      </c>
-      <c r="E31" s="24">
-        <f>D31*E29</f>
-        <v>1.2E-2</v>
+        <v>52</v>
+      </c>
+      <c r="D31" s="24">
+        <v>0.26700000000000002</v>
+      </c>
+      <c r="E31" s="24" t="e">
+        <f>NA()</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D32" s="24">
+        <v>1</v>
+      </c>
+      <c r="E32" s="24" t="e">
+        <f>D32*E30</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D33" s="24">
+        <v>0.4</v>
+      </c>
+      <c r="E33" s="24" t="e">
+        <f>NA()</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D34" s="24">
+        <v>0.26700000000000002</v>
+      </c>
+      <c r="E34" s="24" t="e">
+        <f>NA()</f>
+        <v>#N/A</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:E1" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
-  <conditionalFormatting sqref="A2:C19 E2:XFD19 A30:C31 E30:E31">
-    <cfRule type="expression" dxfId="6" priority="5">
+  <conditionalFormatting sqref="F2:XFD19">
+    <cfRule type="expression" dxfId="73" priority="165">
       <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A29:E29">
-    <cfRule type="expression" dxfId="5" priority="1">
+  <conditionalFormatting sqref="F1:XFD1">
+    <cfRule type="expression" dxfId="71" priority="180">
       <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:XFD1">
-    <cfRule type="expression" dxfId="4" priority="20">
+  <conditionalFormatting sqref="A35:XFD1048576 F20:XFD34">
+    <cfRule type="expression" dxfId="70" priority="166">
       <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A20:XFD25 A26 C26:XFD26 A27:XFD28 F29:XFD31 A32:XFD1048576">
-    <cfRule type="expression" dxfId="3" priority="6">
-      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D2 D4:D5 D8:D13 D15:D19">
-    <cfRule type="expression" dxfId="2" priority="13">
-      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D4">
-    <cfRule type="dataBar" priority="15">
+  <conditionalFormatting sqref="D35:E1048576">
+    <cfRule type="dataBar" priority="210">
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="2"/>
@@ -3923,8 +4766,33 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D4:D5 D8:D13 D15:D19 D2">
-    <cfRule type="dataBar" priority="19">
+  <conditionalFormatting sqref="A2:C4 E8:E12 A30:C31 E30:E31 E16:E19">
+    <cfRule type="expression" dxfId="30" priority="53">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A29:E29">
+    <cfRule type="expression" dxfId="29" priority="50">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:E1 A5 C5 A6:C19">
+    <cfRule type="expression" dxfId="28" priority="60">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A20:C25 A26 C26 A27:C28 A32:E33">
+    <cfRule type="expression" dxfId="27" priority="54">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D8:D12 D16:D19">
+    <cfRule type="expression" dxfId="26" priority="55">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D8:D12 D16:D19">
+    <cfRule type="dataBar" priority="59">
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="2"/>
@@ -3932,8 +4800,8 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D8:D10 D5 D2 E2:E7">
-    <cfRule type="dataBar" priority="18">
+  <conditionalFormatting sqref="D8:D10">
+    <cfRule type="dataBar" priority="58">
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="2"/>
@@ -3941,8 +4809,8 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D15 D13">
-    <cfRule type="dataBar" priority="14">
+  <conditionalFormatting sqref="D16:D17">
+    <cfRule type="dataBar" priority="57">
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="2"/>
@@ -3950,8 +4818,8 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D15">
-    <cfRule type="dataBar" priority="12">
+  <conditionalFormatting sqref="D18:D19">
+    <cfRule type="dataBar" priority="56">
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="2"/>
@@ -3959,26 +4827,8 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D16:D17">
-    <cfRule type="dataBar" priority="17">
-      <dataBar>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="2"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D18:D19">
-    <cfRule type="dataBar" priority="16">
-      <dataBar>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="2"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="D29">
-    <cfRule type="dataBar" priority="4">
+    <cfRule type="dataBar" priority="52">
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="2"/>
@@ -3986,13 +4836,13 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4A758992-EB2C-4F27-8777-FE76B0D877EB}</x14:id>
+          <x14:id>{1B6702EA-698C-4AB4-AC6B-0250E176426D}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D1:E1 D32:E1048576">
-    <cfRule type="dataBar" priority="50">
+  <conditionalFormatting sqref="D1:E1">
+    <cfRule type="dataBar" priority="65">
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="2"/>
@@ -4000,24 +4850,8 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D20:E28">
-    <cfRule type="dataBar" priority="7">
-      <dataBar>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="2"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-    </cfRule>
-    <cfRule type="dataBar" priority="8">
-      <dataBar>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="2"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="D29:E29 E30:E31">
-    <cfRule type="dataBar" priority="3">
+    <cfRule type="dataBar" priority="51">
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="2"/>
@@ -4025,13 +4859,13 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{AD1A05F7-3D3A-4C88-A34C-CD662DCF98F2}</x14:id>
+          <x14:id>{D95A075A-797B-424A-9857-067CBC75C1E3}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E8:E10">
-    <cfRule type="dataBar" priority="25">
+  <conditionalFormatting sqref="D32:E33">
+    <cfRule type="dataBar" priority="66">
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="2"/>
@@ -4039,8 +4873,8 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E11:E12">
-    <cfRule type="dataBar" priority="28">
+  <conditionalFormatting sqref="E8:E10">
+    <cfRule type="dataBar" priority="63">
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="2"/>
@@ -4048,8 +4882,8 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E13:E15">
-    <cfRule type="dataBar" priority="23">
+  <conditionalFormatting sqref="E11:E12">
+    <cfRule type="dataBar" priority="64">
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="2"/>
@@ -4058,16 +4892,429 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E16:E17">
+    <cfRule type="dataBar" priority="62">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E18:E19">
+    <cfRule type="dataBar" priority="61">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A34:E34">
+    <cfRule type="expression" dxfId="25" priority="48">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D34:E34">
+    <cfRule type="dataBar" priority="49">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:E1">
+    <cfRule type="expression" dxfId="24" priority="46">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A20:C25 A27:C28 A32:E32">
+    <cfRule type="expression" dxfId="23" priority="45">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D1:E1">
+    <cfRule type="dataBar" priority="47">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A5 A6:C19 D8:E12 B2:C4 D16:E19">
+    <cfRule type="expression" dxfId="22" priority="39">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B21:C25 C26 B27:C27">
+    <cfRule type="expression" dxfId="21" priority="36">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B20:C20 A26:A28">
+    <cfRule type="expression" dxfId="20" priority="37">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C5">
+    <cfRule type="expression" dxfId="19" priority="34">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D8:D10">
+    <cfRule type="dataBar" priority="43">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{4D694FE1-6491-4FE7-BA24-2CB63A5C1B2A}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D8:D12 D16:D19">
+    <cfRule type="dataBar" priority="38">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{4948CC46-32E9-4C74-8223-41FC3084A93C}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D11:E12">
+    <cfRule type="dataBar" priority="44">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{13580D0E-CA7E-411B-8081-2FE66BCE03EA}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D16:E17">
+    <cfRule type="dataBar" priority="41">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{4DFED52D-2141-4521-9848-703CE9EFE571}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D18:E19">
+    <cfRule type="dataBar" priority="40">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{A4D8761B-AE15-4E55-9A88-9947F767ABD5}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E8:E10">
+    <cfRule type="dataBar" priority="42">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{EDC38D59-6F8C-4D18-B0F9-A98AAE4DCB84}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E29:E34">
+    <cfRule type="expression" dxfId="18" priority="33">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B28:C28">
+    <cfRule type="expression" dxfId="17" priority="35">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2:A4">
+    <cfRule type="expression" dxfId="16" priority="32">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A29:A31">
+    <cfRule type="expression" dxfId="15" priority="31">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A32:A34">
+    <cfRule type="expression" dxfId="14" priority="30">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C29 B30:C30">
+    <cfRule type="expression" dxfId="13" priority="28">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E29">
+    <cfRule type="dataBar" priority="27">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{36416918-565C-4112-A06B-56D1C4C57D87}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E30">
+    <cfRule type="dataBar" priority="29">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{5C6AB91E-41B7-407E-A401-FE1504D3F606}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E31">
+    <cfRule type="dataBar" priority="26">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{2FEC0D0F-524F-4CC4-933C-9F0DE98239EB}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B31:C31">
+    <cfRule type="expression" dxfId="12" priority="25">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C32 B33:C33">
+    <cfRule type="expression" dxfId="11" priority="23">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E32">
     <cfRule type="dataBar" priority="22">
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="2"/>
         <color rgb="FF638EC6"/>
       </dataBar>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E18:E19">
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{1E5B84CC-5BC2-4027-92C6-1AFE3EFAAF0B}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E33">
+    <cfRule type="dataBar" priority="24">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{FF5121CC-70FC-40D8-8326-38DDB09320F5}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E34">
     <cfRule type="dataBar" priority="21">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{3DE1DEF4-D2C5-4292-91E4-BCFBB93D3286}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B34:C34">
+    <cfRule type="expression" dxfId="10" priority="20">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A20:A22">
+    <cfRule type="expression" dxfId="9" priority="19">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A23:A25">
+    <cfRule type="expression" dxfId="8" priority="18">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D29:D34">
+    <cfRule type="expression" dxfId="7" priority="16">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D29:D34">
+    <cfRule type="dataBar" priority="15">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{9C01C7D7-7D10-472D-8AE2-8B38FF6D130D}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D29:D34">
+    <cfRule type="dataBar" priority="17">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{995B14BF-1068-4BF9-B0B9-4494A505D5E8}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D20:E28">
+    <cfRule type="expression" dxfId="6" priority="12">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D20:E28">
+    <cfRule type="dataBar" priority="13">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+    </cfRule>
+    <cfRule type="dataBar" priority="14">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:E7">
+    <cfRule type="expression" dxfId="5" priority="7">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D2 D4:D5">
+    <cfRule type="expression" dxfId="4" priority="8">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D4">
+    <cfRule type="dataBar" priority="9">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D4:D5 D2">
+    <cfRule type="dataBar" priority="11">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D2 D5 E2:E7">
+    <cfRule type="dataBar" priority="10">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E13:E15">
+    <cfRule type="expression" dxfId="3" priority="1">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D13 D15">
+    <cfRule type="expression" dxfId="2" priority="3">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D15 D13">
+    <cfRule type="dataBar" priority="5">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D13 D15">
+    <cfRule type="dataBar" priority="4">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D15">
+    <cfRule type="dataBar" priority="2">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E13:E15">
+    <cfRule type="dataBar" priority="6">
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="2"/>
@@ -4085,7 +5332,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{4A758992-EB2C-4F27-8777-FE76B0D877EB}">
+          <x14:cfRule type="dataBar" id="{1B6702EA-698C-4AB4-AC6B-0250E176426D}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -4100,7 +5347,7 @@
           <xm:sqref>D29</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{AD1A05F7-3D3A-4C88-A34C-CD662DCF98F2}">
+          <x14:cfRule type="dataBar" id="{D95A075A-797B-424A-9857-067CBC75C1E3}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -4113,6 +5360,216 @@
             </x14:dataBar>
           </x14:cfRule>
           <xm:sqref>D29:E29 E30:E31</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{4D694FE1-6491-4FE7-BA24-2CB63A5C1B2A}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>2</xm:f>
+              </x14:cfvo>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>D8:D10</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{4948CC46-32E9-4C74-8223-41FC3084A93C}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>2</xm:f>
+              </x14:cfvo>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>D8:D12 D16:D19</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{13580D0E-CA7E-411B-8081-2FE66BCE03EA}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>2</xm:f>
+              </x14:cfvo>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>D11:E12</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{4DFED52D-2141-4521-9848-703CE9EFE571}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>2</xm:f>
+              </x14:cfvo>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>D16:E17</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{A4D8761B-AE15-4E55-9A88-9947F767ABD5}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>2</xm:f>
+              </x14:cfvo>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>D18:E19</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{EDC38D59-6F8C-4D18-B0F9-A98AAE4DCB84}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>2</xm:f>
+              </x14:cfvo>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>E8:E10</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{36416918-565C-4112-A06B-56D1C4C57D87}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>2</xm:f>
+              </x14:cfvo>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>E29</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{5C6AB91E-41B7-407E-A401-FE1504D3F606}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>2</xm:f>
+              </x14:cfvo>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>E30</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{2FEC0D0F-524F-4CC4-933C-9F0DE98239EB}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>2</xm:f>
+              </x14:cfvo>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>E31</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{1E5B84CC-5BC2-4027-92C6-1AFE3EFAAF0B}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>2</xm:f>
+              </x14:cfvo>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>E32</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{FF5121CC-70FC-40D8-8326-38DDB09320F5}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>2</xm:f>
+              </x14:cfvo>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>E33</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{3DE1DEF4-D2C5-4292-91E4-BCFBB93D3286}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>2</xm:f>
+              </x14:cfvo>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>E34</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{9C01C7D7-7D10-472D-8AE2-8B38FF6D130D}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>2</xm:f>
+              </x14:cfvo>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>D29:D34</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{995B14BF-1068-4BF9-B0B9-4494A505D5E8}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>2</xm:f>
+              </x14:cfvo>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>D29:D34</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -4144,19 +5601,19 @@
   <sheetData>
     <row r="1" spans="1:15">
       <c r="A1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B1" t="s">
         <v>54</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>55</v>
-      </c>
-      <c r="C1" t="s">
-        <v>56</v>
       </c>
       <c r="D1" t="s">
         <v>13</v>
       </c>
       <c r="E1" s="18" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F1" s="17" t="s">
         <v>35</v>
@@ -4180,13 +5637,13 @@
         <v>40</v>
       </c>
       <c r="M1" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N1" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="N1" s="16" t="s">
+      <c r="O1" s="16" t="s">
         <v>59</v>
-      </c>
-      <c r="O1" s="16" t="s">
-        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -4248,46 +5705,46 @@
         <v>12</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D1" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="E1" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="E1" s="17" t="s">
+      <c r="F1" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="F1" s="17" t="s">
+      <c r="G1" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="G1" s="17" t="s">
+      <c r="H1" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="H1" s="16" t="s">
+      <c r="I1" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="I1" s="16" t="s">
+      <c r="J1" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="J1" s="17" t="s">
+      <c r="K1" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="K1" s="16" t="s">
+      <c r="L1" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="L1" s="17" t="s">
+      <c r="M1" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="M1" s="16" t="s">
+      <c r="N1" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="N1" s="16" t="s">
+      <c r="O1" s="16" t="s">
         <v>72</v>
-      </c>
-      <c r="O1" s="16" t="s">
-        <v>73</v>
       </c>
       <c r="P1" s="16" t="s">
         <v>39</v>
@@ -4296,13 +5753,13 @@
         <v>40</v>
       </c>
       <c r="R1" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="S1" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="S1" s="16" t="s">
+      <c r="T1" s="36" t="s">
         <v>75</v>
-      </c>
-      <c r="T1" s="36" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="2" spans="1:20">
@@ -4310,7 +5767,7 @@
         <v>11</v>
       </c>
       <c r="B2" s="39" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C2" s="39" t="s">
         <v>20</v>
@@ -4370,7 +5827,7 @@
         <v>11</v>
       </c>
       <c r="B3" s="39" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C3" s="39" t="s">
         <v>20</v>
@@ -4431,7 +5888,7 @@
         <v>11</v>
       </c>
       <c r="B4" s="47" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C4" s="39" t="s">
         <v>20</v>
@@ -4544,19 +6001,19 @@
         <v>13</v>
       </c>
       <c r="C1" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="D1" s="34" t="s">
+        <v>56</v>
+      </c>
+      <c r="E1" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="D1" s="34" t="s">
-        <v>57</v>
-      </c>
-      <c r="E1" s="17" t="s">
+      <c r="F1" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="F1" s="17" t="s">
+      <c r="G1" s="17" t="s">
         <v>82</v>
-      </c>
-      <c r="G1" s="17" t="s">
-        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -4599,10 +6056,10 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>84</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -4617,7 +6074,7 @@
       <c r="A3" s="5">
         <v>1</v>
       </c>
-      <c r="B3" s="64">
+      <c r="B3" s="62">
         <v>565916667</v>
       </c>
     </row>
@@ -4625,7 +6082,7 @@
       <c r="A4" s="2">
         <v>2</v>
       </c>
-      <c r="B4" s="64">
+      <c r="B4" s="62">
         <v>565916667</v>
       </c>
     </row>
@@ -4633,7 +6090,7 @@
       <c r="A5" s="2">
         <v>3</v>
       </c>
-      <c r="B5" s="64">
+      <c r="B5" s="62">
         <v>565916667</v>
       </c>
     </row>
@@ -4641,7 +6098,7 @@
       <c r="A6" s="2">
         <v>4</v>
       </c>
-      <c r="B6" s="64">
+      <c r="B6" s="62">
         <v>565916667</v>
       </c>
     </row>
@@ -4649,7 +6106,7 @@
       <c r="A7" s="2">
         <v>5</v>
       </c>
-      <c r="B7" s="64">
+      <c r="B7" s="62">
         <v>565916667</v>
       </c>
     </row>
@@ -4657,7 +6114,7 @@
       <c r="A8" s="2">
         <v>6</v>
       </c>
-      <c r="B8" s="64">
+      <c r="B8" s="62">
         <v>565916667</v>
       </c>
     </row>
@@ -4665,7 +6122,7 @@
       <c r="A9" s="2">
         <v>7</v>
       </c>
-      <c r="B9" s="64">
+      <c r="B9" s="62">
         <v>565916667</v>
       </c>
     </row>
@@ -4673,7 +6130,7 @@
       <c r="A10" s="2">
         <v>8</v>
       </c>
-      <c r="B10" s="64">
+      <c r="B10" s="62">
         <v>565916667</v>
       </c>
     </row>
@@ -4681,7 +6138,7 @@
       <c r="A11" s="2">
         <v>9</v>
       </c>
-      <c r="B11" s="64">
+      <c r="B11" s="62">
         <v>565916667</v>
       </c>
     </row>
@@ -4689,7 +6146,7 @@
       <c r="A12" s="2">
         <v>10</v>
       </c>
-      <c r="B12" s="64">
+      <c r="B12" s="62">
         <v>565916667</v>
       </c>
     </row>
@@ -4697,7 +6154,7 @@
       <c r="A13" s="2">
         <v>11</v>
       </c>
-      <c r="B13" s="64">
+      <c r="B13" s="62">
         <v>565916667</v>
       </c>
     </row>
@@ -4705,7 +6162,7 @@
       <c r="A14" s="2">
         <v>12</v>
       </c>
-      <c r="B14" s="64">
+      <c r="B14" s="62">
         <v>565916667</v>
       </c>
     </row>
